--- a/artfynd/A 54693-2022 artfynd.xlsx
+++ b/artfynd/A 54693-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54693-2022 artfynd.xlsx
+++ b/artfynd/A 54693-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105228200</v>
+        <v>105225923</v>
       </c>
       <c r="B2" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6459</v>
+        <v>283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404508.333055294</v>
+        <v>404530</v>
       </c>
       <c r="R2" t="n">
-        <v>7062366.041692726</v>
+        <v>7062349</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,76 +746,62 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
+          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105225929</v>
+        <v>105225934</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404643.433394062</v>
+        <v>404586</v>
       </c>
       <c r="R3" t="n">
-        <v>7062421.920263164</v>
+        <v>7062480</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,19 +847,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105225926</v>
+        <v>105225937</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404533.53819593</v>
+        <v>404798</v>
       </c>
       <c r="R4" t="n">
-        <v>7062361.283275754</v>
+        <v>7062613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,19 +948,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105228196</v>
+        <v>105228188</v>
       </c>
       <c r="B5" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404546.1241344312</v>
+        <v>404755</v>
       </c>
       <c r="R5" t="n">
-        <v>7062380.444809561</v>
+        <v>7062551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1046,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105225931</v>
+        <v>105228191</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,37 +1086,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404640.4035814627</v>
+        <v>404604</v>
       </c>
       <c r="R6" t="n">
-        <v>7062424.676370193</v>
+        <v>7062497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,55 +1143,39 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
+          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105225940</v>
+        <v>105228203</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,37 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404777.5348340048</v>
+        <v>404488</v>
       </c>
       <c r="R7" t="n">
-        <v>7062651.475567455</v>
+        <v>7062369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,93 +1240,74 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
+          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105225925</v>
+        <v>105228190</v>
       </c>
       <c r="B8" t="n">
-        <v>73624</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1776</v>
+        <v>306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amerikansk sönderfallslav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bactrospora brodoi</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Egea &amp; Torrente</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404535.3824413107</v>
+        <v>404669</v>
       </c>
       <c r="R8" t="n">
-        <v>7062363.448223795</v>
+        <v>7062561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,55 +1337,39 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
+          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105225936</v>
+        <v>105225921</v>
       </c>
       <c r="B9" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,21 +1377,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404787.5153837223</v>
+        <v>404476</v>
       </c>
       <c r="R9" t="n">
-        <v>7062569.462140553</v>
+        <v>7062387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,19 +1437,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,15 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105225937</v>
+        <v>105228205</v>
       </c>
       <c r="B10" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1638,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404798.1548919444</v>
+        <v>404467</v>
       </c>
       <c r="R10" t="n">
-        <v>7062612.662880634</v>
+        <v>7062392</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,19 +1538,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,68 +1553,75 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe # Betula pubescens</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
+          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105225924</v>
+        <v>105228196</v>
       </c>
       <c r="B11" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404519.4830919818</v>
+        <v>404547</v>
       </c>
       <c r="R11" t="n">
-        <v>7062352.381040529</v>
+        <v>7062380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,55 +1651,39 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
+          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105225932</v>
+        <v>105228204</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,42 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404571.8111220318</v>
+        <v>404486</v>
       </c>
       <c r="R12" t="n">
-        <v>7062480.040071323</v>
+        <v>7062379</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1748,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,62 +1765,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105228192</v>
+        <v>105225925</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1776</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Amerikansk sönderfallslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bactrospora brodoi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404605.6554643791</v>
+        <v>404535</v>
       </c>
       <c r="R13" t="n">
-        <v>7062496.338852638</v>
+        <v>7062364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,89 +1848,78 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
+          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105228193</v>
+        <v>105225929</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404585.7700884083</v>
+        <v>404644</v>
       </c>
       <c r="R14" t="n">
-        <v>7062412.113062245</v>
+        <v>7062422</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,76 +1949,62 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
+          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105225938</v>
+        <v>105225924</v>
       </c>
       <c r="B15" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2214,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404783.0628666868</v>
+        <v>404520</v>
       </c>
       <c r="R15" t="n">
-        <v>7062613.561548614</v>
+        <v>7062352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,19 +2050,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,37 +2080,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105225921</v>
+        <v>105225927</v>
       </c>
       <c r="B16" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6428</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2330,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404476.0439840478</v>
+        <v>404597</v>
       </c>
       <c r="R16" t="n">
-        <v>7062386.558783421</v>
+        <v>7062410</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,19 +2151,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,53 +2181,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105228199</v>
+        <v>105228187</v>
       </c>
       <c r="B17" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6486</v>
+        <v>6428</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404510.554611198</v>
+        <v>404791</v>
       </c>
       <c r="R17" t="n">
-        <v>7062365.974587619</v>
+        <v>7062583</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,50 +2249,19 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Mikroskoperad, bål med trebouxida alger</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2539,15 +2278,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105228186</v>
+        <v>105228194</v>
       </c>
       <c r="B18" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,21 +2289,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2579,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404795.3054341951</v>
+        <v>404586</v>
       </c>
       <c r="R18" t="n">
-        <v>7062591.876366681</v>
+        <v>7062412</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2612,19 +2346,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,15 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105225923</v>
+        <v>105225926</v>
       </c>
       <c r="B19" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,10 +2413,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404529.5950900881</v>
+        <v>404533</v>
       </c>
       <c r="R19" t="n">
-        <v>7062348.52260392</v>
+        <v>7062362</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,19 +2446,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,15 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105225922</v>
+        <v>105225938</v>
       </c>
       <c r="B20" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2783,21 +2487,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2810,10 +2514,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>404520.6016047046</v>
+        <v>404783</v>
       </c>
       <c r="R20" t="n">
-        <v>7062345.241173649</v>
+        <v>7062613</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,19 +2547,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,58 +2577,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105225928</v>
+        <v>105228186</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404624.8956747755</v>
+        <v>404795</v>
       </c>
       <c r="R21" t="n">
-        <v>7062411.820627429</v>
+        <v>7062591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,19 +2645,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,27 +2662,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
+          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>105228190</v>
+        <v>105228200</v>
       </c>
       <c r="B22" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3019,21 +2685,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>306</v>
+        <v>6459</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3043,10 +2709,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404668.9482931095</v>
+        <v>404508</v>
       </c>
       <c r="R22" t="n">
-        <v>7062560.156849897</v>
+        <v>7062366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3076,19 +2742,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,50 +2771,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105228194</v>
+        <v>105228199</v>
       </c>
       <c r="B23" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>6486</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404585.7700884083</v>
+        <v>404510</v>
       </c>
       <c r="R23" t="n">
-        <v>7062412.113062245</v>
+        <v>7062366</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,19 +2842,14 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mikroskoperad, bål med trebouxida alger</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,8 +2858,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3227,50 +2892,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105228187</v>
+        <v>105225928</v>
       </c>
       <c r="B24" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404790.581998778</v>
+        <v>404625</v>
       </c>
       <c r="R24" t="n">
-        <v>7062582.692651754</v>
+        <v>7062411</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3300,19 +2968,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,27 +2985,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
+          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105228195</v>
+        <v>105225932</v>
       </c>
       <c r="B25" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,34 +3008,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404546.1241344312</v>
+        <v>404572</v>
       </c>
       <c r="R25" t="n">
-        <v>7062380.444809561</v>
+        <v>7062480</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,19 +3073,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,27 +3090,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105228203</v>
+        <v>105228192</v>
       </c>
       <c r="B26" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3467,21 +3113,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3491,10 +3137,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404488.4060848487</v>
+        <v>404606</v>
       </c>
       <c r="R26" t="n">
-        <v>7062368.864323462</v>
+        <v>7062496</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3524,19 +3170,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,37 +3199,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105225927</v>
+        <v>105225922</v>
       </c>
       <c r="B27" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3606,10 +3237,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404597.7261409651</v>
+        <v>404521</v>
       </c>
       <c r="R27" t="n">
-        <v>7062410.419855643</v>
+        <v>7062346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3639,19 +3270,9 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3679,15 +3300,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105228191</v>
+        <v>105225936</v>
       </c>
       <c r="B28" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3695,34 +3311,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nordböle, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404603.4607809881</v>
+        <v>404788</v>
       </c>
       <c r="R28" t="n">
-        <v>7062497.293301004</v>
+        <v>7062569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,513 +3371,33 @@
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-12-11</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
+          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>105228204</v>
-      </c>
-      <c r="B29" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Nordböle, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>404486.0351646732</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7062378.706753666</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>105228188</v>
-      </c>
-      <c r="B30" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>283</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Hypogymnia hultenii</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Nordböle, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>404754.9521969345</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7062551.346906692</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>105228205</v>
-      </c>
-      <c r="B31" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>308</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Nordböle, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>404466.8610114697</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7062391.721656688</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe # Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein, Linda Johannesson, Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>105225934</v>
-      </c>
-      <c r="B32" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>283</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Hypogymnia hultenii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Nordböle, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>404586.0419581957</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7062480.054614468</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-12-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Linda Johannesson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Linda Johannesson, Jesper Wadstein, Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54693-2022 artfynd.xlsx
+++ b/artfynd/A 54693-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225934</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225937</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228191</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228203</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228190</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225921</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1580,6 +1625,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228205</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228196</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228204</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1875,6 +1935,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225925</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1976,6 +2041,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225929</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2077,6 +2147,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225924</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2178,6 +2253,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225927</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2275,6 +2355,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228187</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2372,6 +2457,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228194</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2473,6 +2563,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225926</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2574,6 +2669,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225938</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2671,6 +2771,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228186</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2768,6 +2873,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228200</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228199</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2994,6 +3109,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225928</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3099,6 +3219,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225932</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3196,6 +3321,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228192</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3297,6 +3427,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225922</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3398,8 +3533,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105225936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>